--- a/data/trans_orig/Q61A-Clase-trans_orig.xlsx
+++ b/data/trans_orig/Q61A-Clase-trans_orig.xlsx
@@ -526,7 +526,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Número medio de meses que lleva en paro</t>
+          <t>Número medio de meses que lleva en paro (tasa de respuesta: 95,13%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -716,62 +716,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>2,94; 6,7</t>
+          <t>2,94; 6,6</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>12,13; 19,59</t>
+          <t>12,27; 19,66</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>11,9; 22,19</t>
+          <t>12,14; 21,73</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>10,54; 31,44</t>
+          <t>10,36; 30,2</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>4,54; 53,59</t>
+          <t>5,01; 61,94</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>9,48; 15,72</t>
+          <t>9,36; 16,05</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>17,71; 32,22</t>
+          <t>17,57; 32,48</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>13,77; 33,36</t>
+          <t>13,53; 32,54</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>4,33; 33,32</t>
+          <t>4,27; 32,17</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>11,54; 16,25</t>
+          <t>11,52; 16,27</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>15,99; 25,37</t>
+          <t>16,57; 25,63</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>13,88; 27,56</t>
+          <t>13,27; 27,11</t>
         </is>
       </c>
     </row>
@@ -861,57 +861,57 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>9,6; 19,43</t>
+          <t>9,79; 18,87</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>17,27; 27,14</t>
+          <t>17,23; 27,52</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>13,3; 31,94</t>
+          <t>13,46; 32,95</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>3,92; 15,29</t>
+          <t>3,85; 14,28</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>16,35; 25,69</t>
+          <t>16,29; 25,17</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>20,91; 30,25</t>
+          <t>21,29; 30,33</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>19,21; 37,42</t>
+          <t>19,09; 34,9</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>5,08; 20,69</t>
+          <t>4,84; 21,25</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>14,58; 21,05</t>
+          <t>14,34; 21,4</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>21,13; 27,97</t>
+          <t>20,92; 28,11</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>19,05; 31,95</t>
+          <t>18,74; 32,28</t>
         </is>
       </c>
     </row>
@@ -996,62 +996,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>2,75; 8,83</t>
+          <t>2,77; 9,99</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>17,22; 28,18</t>
+          <t>17,36; 28,1</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>19,69; 29,16</t>
+          <t>20,18; 28,81</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>29,22; 57,02</t>
+          <t>27,36; 53,7</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>2,9; 8,76</t>
+          <t>2,95; 8,9</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>20,53; 33,73</t>
+          <t>20,96; 33,86</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>28,17; 62,8</t>
+          <t>28,59; 60,47</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>29,42; 63,19</t>
+          <t>29,26; 64,02</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>3,54; 7,84</t>
+          <t>3,59; 7,98</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>18,67; 27,87</t>
+          <t>18,89; 27,63</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>22,89; 32,49</t>
+          <t>23,12; 32,69</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>31,02; 54,07</t>
+          <t>30,88; 53,55</t>
         </is>
       </c>
     </row>
@@ -1136,62 +1136,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>4,66; 7,45</t>
+          <t>4,66; 7,51</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>11,46; 14,41</t>
+          <t>11,49; 14,36</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>18,12; 23,64</t>
+          <t>18,07; 23,36</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>14,14; 23,63</t>
+          <t>14,09; 23,53</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>5,55; 11,57</t>
+          <t>5,46; 11,08</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>16,71; 26,38</t>
+          <t>16,71; 26,33</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>18,91; 26,74</t>
+          <t>18,72; 26,18</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>18,5; 32,61</t>
+          <t>18,31; 31,44</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>5,39; 8,28</t>
+          <t>5,33; 8,24</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>14,06; 18,15</t>
+          <t>14,05; 18,53</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>19,18; 23,53</t>
+          <t>19,09; 23,6</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>17,51; 25,88</t>
+          <t>17,52; 25,18</t>
         </is>
       </c>
     </row>
@@ -1276,62 +1276,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>4,4; 7,62</t>
+          <t>4,24; 7,59</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>12,03; 16,46</t>
+          <t>12,03; 16,15</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>13,34; 19,48</t>
+          <t>13,17; 19,69</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>10,81; 21,83</t>
+          <t>11,27; 23,32</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>6,2; 9,11</t>
+          <t>6,17; 9,28</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>12,69; 17,6</t>
+          <t>12,82; 17,69</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>16,89; 24,36</t>
+          <t>17,07; 24,46</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>17,1; 28,22</t>
+          <t>16,77; 27,4</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>5,69; 7,82</t>
+          <t>5,61; 7,95</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>12,81; 16,19</t>
+          <t>12,93; 16,19</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>16,01; 21,1</t>
+          <t>15,71; 20,8</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>15,69; 23,37</t>
+          <t>15,83; 23,31</t>
         </is>
       </c>
     </row>
@@ -1451,7 +1451,7 @@
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>5,74; 10,42</t>
+          <t>6,48; 11,01</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
@@ -1471,7 +1471,7 @@
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>6,19; 11,41</t>
+          <t>6,47; 11,74</t>
         </is>
       </c>
     </row>
@@ -1556,62 +1556,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>5,02; 8,89</t>
+          <t>5,08; 8,78</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>13,74; 16,59</t>
+          <t>13,74; 16,52</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>18,12; 21,33</t>
+          <t>18,23; 21,43</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>16,83; 23,82</t>
+          <t>16,81; 23,63</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>6,37; 11,57</t>
+          <t>6,21; 10,69</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>16,38; 20,92</t>
+          <t>16,35; 21,01</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>20,54; 25,21</t>
+          <t>20,8; 25,22</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>20,39; 27,03</t>
+          <t>20,3; 26,93</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>5,95; 8,68</t>
+          <t>5,93; 8,74</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>15,28; 17,63</t>
+          <t>15,25; 17,63</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>19,8; 22,59</t>
+          <t>19,8; 22,52</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>19,51; 24,44</t>
+          <t>19,84; 24,54</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/Q61A-Clase-trans_orig.xlsx
+++ b/data/trans_orig/Q61A-Clase-trans_orig.xlsx
@@ -663,7 +663,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>18,3</t>
+          <t>18,55</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -683,7 +683,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>20,8</t>
+          <t>20,75</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -703,7 +703,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>19,61</t>
+          <t>19,76</t>
         </is>
       </c>
     </row>
@@ -716,62 +716,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>2,94; 6,6</t>
+          <t>2,99; 6,43</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>12,27; 19,66</t>
+          <t>11,97; 19,09</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>12,14; 21,73</t>
+          <t>12,21; 22,53</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>10,36; 30,2</t>
+          <t>10,45; 30,89</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>5,01; 61,94</t>
+          <t>4,81; 66,05</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>9,36; 16,05</t>
+          <t>9,68; 16,15</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>17,57; 32,48</t>
+          <t>17,86; 32,89</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>13,53; 32,54</t>
+          <t>13,67; 31,03</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>4,27; 32,17</t>
+          <t>4,3; 37,78</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>11,52; 16,27</t>
+          <t>11,71; 16,31</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>16,57; 25,63</t>
+          <t>16,44; 25,98</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>13,27; 27,11</t>
+          <t>13,99; 26,86</t>
         </is>
       </c>
     </row>
@@ -803,7 +803,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>20,75</t>
+          <t>19,16</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -823,7 +823,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>25,71</t>
+          <t>28,99</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -843,7 +843,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>24,29</t>
+          <t>26,13</t>
         </is>
       </c>
     </row>
@@ -856,62 +856,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>4,27; 58,9</t>
+          <t>4,14; 60,87</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>9,79; 18,87</t>
+          <t>9,74; 19,12</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>17,23; 27,52</t>
+          <t>17,47; 27,54</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>13,46; 32,95</t>
+          <t>12,48; 30,53</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>3,85; 14,28</t>
+          <t>3,94; 15,14</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>16,29; 25,17</t>
+          <t>16,49; 26,63</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>21,29; 30,33</t>
+          <t>21,39; 30,33</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>19,09; 34,9</t>
+          <t>21,08; 41,43</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>4,84; 21,25</t>
+          <t>4,77; 17,83</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>14,34; 21,4</t>
+          <t>14,51; 21,29</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>20,92; 28,11</t>
+          <t>21,07; 27,92</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>18,74; 32,28</t>
+          <t>19,64; 34,52</t>
         </is>
       </c>
     </row>
@@ -943,7 +943,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>39,3</t>
+          <t>33,66</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -963,7 +963,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>42,73</t>
+          <t>39,0</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -983,7 +983,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>40,44</t>
+          <t>35,32</t>
         </is>
       </c>
     </row>
@@ -996,62 +996,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>2,77; 9,99</t>
+          <t>2,91; 9,24</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>17,36; 28,1</t>
+          <t>17,51; 28,15</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>20,18; 28,81</t>
+          <t>19,92; 29,11</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>27,36; 53,7</t>
+          <t>23,2; 48,47</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>2,95; 8,9</t>
+          <t>3,09; 8,97</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>20,96; 33,86</t>
+          <t>20,75; 32,77</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>28,59; 60,47</t>
+          <t>29,12; 62,48</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>29,26; 64,02</t>
+          <t>26,42; 60,28</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>3,59; 7,98</t>
+          <t>3,47; 7,82</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>18,89; 27,63</t>
+          <t>18,79; 27,98</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>23,12; 32,69</t>
+          <t>22,74; 32,32</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>30,88; 53,55</t>
+          <t>26,14; 47,34</t>
         </is>
       </c>
     </row>
@@ -1083,7 +1083,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>17,94</t>
+          <t>18,19</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1103,7 +1103,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>23,56</t>
+          <t>24,04</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1123,7 +1123,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>20,75</t>
+          <t>21,21</t>
         </is>
       </c>
     </row>
@@ -1141,57 +1141,57 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>11,49; 14,36</t>
+          <t>11,41; 14,22</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>18,07; 23,36</t>
+          <t>18,16; 23,67</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>14,09; 23,53</t>
+          <t>14,63; 23,67</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>5,46; 11,08</t>
+          <t>5,51; 10,91</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>16,71; 26,33</t>
+          <t>16,72; 26,31</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>18,72; 26,18</t>
+          <t>18,66; 26,71</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>18,31; 31,44</t>
+          <t>19,23; 31,46</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>5,33; 8,24</t>
+          <t>5,38; 8,28</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>14,05; 18,53</t>
+          <t>14,14; 18,47</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>19,09; 23,6</t>
+          <t>19,13; 23,56</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>17,52; 25,18</t>
+          <t>18,27; 26,94</t>
         </is>
       </c>
     </row>
@@ -1223,7 +1223,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>15,5</t>
+          <t>15,22</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1243,7 +1243,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>20,86</t>
+          <t>20,34</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1263,7 +1263,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>18,92</t>
+          <t>18,45</t>
         </is>
       </c>
     </row>
@@ -1276,69 +1276,69 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>4,24; 7,59</t>
+          <t>4,29; 7,57</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>12,03; 16,15</t>
+          <t>12,11; 16,29</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>13,17; 19,69</t>
+          <t>13,24; 19,27</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>11,27; 23,32</t>
+          <t>11,38; 20,91</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>6,17; 9,28</t>
+          <t>6,15; 9,22</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>12,82; 17,69</t>
+          <t>12,64; 17,89</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>17,07; 24,46</t>
+          <t>16,57; 24,41</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>16,77; 27,4</t>
+          <t>16,61; 27,45</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>5,61; 7,95</t>
+          <t>5,62; 7,86</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>12,93; 16,19</t>
+          <t>12,79; 16,06</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>15,71; 20,8</t>
+          <t>16,07; 21,1</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>15,83; 23,31</t>
+          <t>15,55; 22,76</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -1383,7 +1383,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>8,95</t>
+          <t>8,9</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -1403,7 +1403,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>9,4</t>
+          <t>12,23</t>
         </is>
       </c>
     </row>
@@ -1451,7 +1451,7 @@
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>6,48; 11,01</t>
+          <t>5,78; 11,0</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
@@ -1471,7 +1471,7 @@
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>6,47; 11,74</t>
+          <t>7,98; 16,87</t>
         </is>
       </c>
     </row>
@@ -1503,7 +1503,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>19,96</t>
+          <t>19,43</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1523,7 +1523,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>23,28</t>
+          <t>23,49</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -1543,7 +1543,7 @@
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>21,82</t>
+          <t>21,71</t>
         </is>
       </c>
     </row>
@@ -1556,62 +1556,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>5,08; 8,78</t>
+          <t>5,02; 8,57</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>13,74; 16,52</t>
+          <t>13,76; 16,62</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>18,23; 21,43</t>
+          <t>18,09; 21,41</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>16,81; 23,63</t>
+          <t>16,67; 22,78</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>6,21; 10,69</t>
+          <t>6,23; 11,24</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>16,35; 21,01</t>
+          <t>16,42; 20,71</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>20,8; 25,22</t>
+          <t>20,77; 25,34</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>20,3; 26,93</t>
+          <t>20,66; 27,54</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>5,93; 8,74</t>
+          <t>5,91; 8,75</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>15,25; 17,63</t>
+          <t>15,23; 17,64</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>19,8; 22,52</t>
+          <t>19,72; 22,55</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>19,84; 24,54</t>
+          <t>19,52; 24,15</t>
         </is>
       </c>
     </row>
